--- a/supp/Supplementary_Table_S5_Clinical_PUBLICATION.xlsx
+++ b/supp/Supplementary_Table_S5_Clinical_PUBLICATION.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1_Cohort_definition" sheetId="1" r:id="R2cc7883b46794b60"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2_Patient_scores" sheetId="2" r:id="Rc5927a18e234488f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3_Program146_mapping" sheetId="3" r:id="R745017770f2f4b3e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4_Clinical_models" sheetId="4" r:id="R49d06d8f4e0b40a5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5_Incremental_model" sheetId="5" r:id="R8eba4143cc354165"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6_RNA_quantification" sheetId="6" r:id="R0f7ee596c9604bef"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7_Score_definition" sheetId="7" r:id="R859a88e7114e45cb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1_Cohort_definition" sheetId="1" r:id="R929f8052ea8e4634"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2_Patient_scores" sheetId="2" r:id="R9d8f59d922a04147"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3_Program146_mapping" sheetId="3" r:id="Rc5ac7770cf704b23"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4_Clinical_models" sheetId="4" r:id="Rd223a128d11f4888"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5_Incremental_model" sheetId="5" r:id="Rfec402d48075470d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6_RNA_quantification" sheetId="6" r:id="R82604443524f40f0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7_Score_definition" sheetId="7" r:id="R47276a789aea4db4"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -449,7 +449,7 @@
         <x:v>D definition</x:v>
       </x:c>
       <x:c r="B12" s="3" t="str">
-        <x:v>Residual disease after NAC; distant metastasis within 2 years of curative surgery</x:v>
+        <x:v>Distant metastasis within 2 years after surgery</x:v>
       </x:c>
       <x:c r="C12" s="3" t="str">
         <x:v>https://doi.org/10.1016/j.xcrm.2025.102164</x:v>
@@ -460,7 +460,7 @@
         <x:v>ND definition</x:v>
       </x:c>
       <x:c r="B13" s="3" t="str">
-        <x:v>Residual disease after NAC; no recurrence. The source cohort reported no disease progression or breast-cancer-specific death during 7 years of follow-up</x:v>
+        <x:v>No recurrence, disease progression or breast-cancer-specific death during 7-year follow-up</x:v>
       </x:c>
       <x:c r="C13" s="3" t="str">
         <x:v>https://doi.org/10.1016/j.xcrm.2025.102164</x:v>
@@ -493,7 +493,7 @@
         <x:v>Design</x:v>
       </x:c>
       <x:c r="B16" s="3" t="str">
-        <x:v>Retrospective extreme-outcome cohort; not an unselected survival cohort or prospective clinical validation</x:v>
+        <x:v>Retrospective extreme-outcome cohort</x:v>
       </x:c>
       <x:c r="C16" s="3" t="str">
         <x:v>https://doi.org/10.1016/j.xcrm.2025.102164</x:v>
@@ -5654,7 +5654,7 @@
   <x:sheetData>
     <x:row r="1" ht="24" customHeight="1">
       <x:c r="A1" s="5" t="str">
-        <x:v>Incremental information beyond RCB class</x:v>
+        <x:v>RCB-adjusted model comparison</x:v>
       </x:c>
       <x:c r="B1" s="6"/>
       <x:c r="C1" s="6"/>
@@ -5823,7 +5823,7 @@
         <x:v>Aggregation</x:v>
       </x:c>
       <x:c r="B12" s="3" t="str">
-        <x:v>Exact GENCODE v36 transcript-to-gene mapping implemented in project code; sum transcript TPM and estimated read counts by gene ID</x:v>
+        <x:v>Exact GENCODE v36 mapping; transcript TPM and estimated read counts summed by gene ID</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="15" hidden="0" customHeight="1">
@@ -5839,7 +5839,7 @@
         <x:v>Quantification workflow</x:v>
       </x:c>
       <x:c r="B14" s="3" t="str">
-        <x:v>Project reprocessing of public WTS reads; distinct from the original study STAR/RSEM processing</x:v>
+        <x:v>Project: Salmon reprocessing. Original study: STAR/RSEM.</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="15" hidden="0" customHeight="1">
